--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1822,42 +1822,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>80845675</v>
+        <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>93191</v>
+        <v>101582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1866,13 +1861,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507653</v>
+        <v>507259</v>
       </c>
       <c r="R11" t="n">
-        <v>6895271</v>
+        <v>6894311</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1896,12 +1891,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1912,58 +1907,57 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>35-årig, tät sandtallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80845675</t>
+          <t>https://artportalen.se/Sighting/136951537</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>80845714</v>
+        <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>93191</v>
+        <v>101582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1853</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1971,24 +1965,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507198</v>
+        <v>507222</v>
       </c>
       <c r="R12" t="n">
-        <v>6894276</v>
+        <v>6894243</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,12 +2001,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,58 +2017,57 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>ca 40-årig tallskog med lav-, al- och björkinslag</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80845714</t>
+          <t>https://artportalen.se/Sighting/136951538</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>80845674</v>
+        <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>101582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2087,24 +2075,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fåssjödal, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507669</v>
+        <v>507232</v>
       </c>
       <c r="R13" t="n">
-        <v>6895244</v>
+        <v>6894304</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2128,12 +2111,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,68 +2127,62 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>35-årig, tät sandtallskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80845674</t>
+          <t>https://artportalen.se/Sighting/136957042</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>80845676</v>
+        <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>93197</v>
+        <v>101582</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1853</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2214,13 +2191,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507644</v>
+        <v>507215</v>
       </c>
       <c r="R14" t="n">
-        <v>6895280</v>
+        <v>6894256</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2244,12 +2221,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2019-10-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,68 +2237,62 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>35-årig, tät sandtallskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80845676</t>
+          <t>https://artportalen.se/Sighting/136957043</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>80845731</v>
+        <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>93209</v>
+        <v>101582</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>1853</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2330,13 +2301,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507510</v>
+        <v>507214</v>
       </c>
       <c r="R15" t="n">
-        <v>6894387</v>
+        <v>6894253</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,12 +2331,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2376,68 +2347,62 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>35-årig sandtallskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80845731</t>
+          <t>https://artportalen.se/Sighting/136957044</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>80845736</v>
+        <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>93235</v>
+        <v>101582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>1853</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mosippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pulsatilla vernalis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2446,13 +2411,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507204</v>
+        <v>507212</v>
       </c>
       <c r="R16" t="n">
-        <v>6894213</v>
+        <v>6894249</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2476,12 +2441,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2019-10-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,25 +2457,1825 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>vägskärning med lavrik, 45-årig sandtallskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957045</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136957046</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>507209</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6894243</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957046</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136957047</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>507207</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6894246</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957047</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136957048</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>507204</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6894246</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957048</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136957049</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>507200</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6894240</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957049</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136957050</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>507203</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6894243</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957050</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136957051</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>507188</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6894221</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957051</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136957052</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>507186</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6894219</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957052</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136957053</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>507191</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6894217</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957053</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136957054</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>507191</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6894215</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957054</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136957055</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1853</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mosippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pulsatilla vernalis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>507188</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6894215</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3 små bestånd</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957055</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>80845675</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>507653</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6895271</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>35-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845675</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>80845714</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>507198</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6894276</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>ca 40-årig tallskog med lav-, al- och björkinslag</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845714</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>80845674</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>507669</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6895244</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>35-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845674</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>80845676</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>507644</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6895280</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2019-10-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>35-årig, tät sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845676</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>80845731</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>507510</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6894387</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2019-10-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2019-10-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>35-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80845731</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>80845736</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fåssjödal, Hls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>507204</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6894213</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2019-10-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2019-10-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>vägskärning med lavrik, 45-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/80845736</t>
         </is>
@@ -2533,6 +4298,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101605</v>
+        <v>101618</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101618</v>
+        <v>101620</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101620</v>
+        <v>101623</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101623</v>
+        <v>101638</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101638</v>
+        <v>101639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101639</v>
+        <v>101644</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101644</v>
+        <v>101647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101647</v>
+        <v>101653</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101653</v>
+        <v>101665</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101665</v>
+        <v>101666</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101666</v>
+        <v>101669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101669</v>
+        <v>101670</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1959-2024 artfynd.xlsx
+++ b/artfynd/S 1959-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>136951537</v>
       </c>
       <c r="B11" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136951538</v>
       </c>
       <c r="B12" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136957042</v>
       </c>
       <c r="B13" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136957043</v>
       </c>
       <c r="B14" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>136957044</v>
       </c>
       <c r="B15" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136957045</v>
       </c>
       <c r="B16" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>136957046</v>
       </c>
       <c r="B17" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>136957047</v>
       </c>
       <c r="B18" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136957048</v>
       </c>
       <c r="B19" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136957049</v>
       </c>
       <c r="B20" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>136957050</v>
       </c>
       <c r="B21" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136957051</v>
       </c>
       <c r="B22" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>136957052</v>
       </c>
       <c r="B23" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>136957053</v>
       </c>
       <c r="B24" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>136957054</v>
       </c>
       <c r="B25" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136957055</v>
       </c>
       <c r="B26" t="n">
-        <v>101670</v>
+        <v>101673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
